--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.55067563021064</v>
+        <v>8.051984789909229</v>
       </c>
       <c r="D2" t="n">
-        <v>31.00195923103056</v>
+        <v>5.037818375042466</v>
       </c>
       <c r="E2" t="n">
-        <v>6.906054541373135</v>
+        <v>1.122233862973134</v>
       </c>
       <c r="F2" t="n">
-        <v>8.578140716168031</v>
+        <v>1.393947866377305</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.88142707090645</v>
+        <v>7.130731899022298</v>
       </c>
       <c r="D3" t="n">
-        <v>43.07829715386899</v>
+        <v>7.000223287503712</v>
       </c>
       <c r="E3" t="n">
-        <v>6.906054541373135</v>
+        <v>1.122233862973134</v>
       </c>
       <c r="F3" t="n">
-        <v>8.578140716168031</v>
+        <v>1.393947866377305</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.7282478836018</v>
+        <v>9.055840281085292</v>
       </c>
       <c r="D4" t="n">
-        <v>55.09202148816168</v>
+        <v>8.952453491826274</v>
       </c>
       <c r="E4" t="n">
-        <v>6.906054541373135</v>
+        <v>1.122233862973134</v>
       </c>
       <c r="F4" t="n">
-        <v>8.578140716168031</v>
+        <v>1.393947866377305</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.97224043714828</v>
+        <v>8.120489071036596</v>
       </c>
       <c r="D5" t="n">
-        <v>50.84702284537622</v>
+        <v>8.262641212373635</v>
       </c>
       <c r="E5" t="n">
-        <v>6.906054541373135</v>
+        <v>1.122233862973134</v>
       </c>
       <c r="F5" t="n">
-        <v>8.578140716168031</v>
+        <v>1.393947866377305</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.71544465946069</v>
+        <v>5.478759757162363</v>
       </c>
       <c r="D6" t="n">
-        <v>33.51156449894688</v>
+        <v>5.445629231078868</v>
       </c>
       <c r="E6" t="n">
-        <v>6.906054541373135</v>
+        <v>1.122233862973134</v>
       </c>
       <c r="F6" t="n">
-        <v>8.578140716168031</v>
+        <v>1.393947866377305</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.21812725263297</v>
+        <v>7.022945678552858</v>
       </c>
       <c r="D7" t="n">
-        <v>43.13937703009965</v>
+        <v>7.010148767391192</v>
       </c>
       <c r="E7" t="n">
-        <v>6.906054541373135</v>
+        <v>1.122233862973134</v>
       </c>
       <c r="F7" t="n">
-        <v>8.578140716168031</v>
+        <v>1.393947866377305</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
